--- a/backend/storage/imports/Master_SBM/Honorarium 30 PENGINAPAN DINAS DALAM NEGERI.xlsx
+++ b/backend/storage/imports/Master_SBM/Honorarium 30 PENGINAPAN DINAS DALAM NEGERI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\imports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\dokumen perkuliahan\kebutuhan magang\Projek magang\DITUGASKAN\SBM\baru\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C060997-0059-4839-88D5-242DEF575408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC26D18-1D2E-40C4-BB97-CAF559E292A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9131C7EB-F8A1-43A4-8925-D23EF0F46CDD}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="47">
   <si>
     <t>NO.</t>
   </si>
@@ -159,25 +159,22 @@
     <t>SATUAN BIAYA PENGINAPAN PERJALANAN DINAS DALAM NEGERI</t>
   </si>
   <si>
-    <t>PEJABAT NEGARA / PEJABAT ESELON I</t>
-  </si>
-  <si>
-    <t>TARIF HOTEL</t>
-  </si>
-  <si>
-    <t>PEJABAT NEGARA LAINNYA / PEJABAT ESELON II</t>
-  </si>
-  <si>
-    <t>PEJABAT ESELON III / GOLONGAN IV</t>
-  </si>
-  <si>
-    <t>PEJABAT ESELON IV / GOLONGAN III  / II / I</t>
-  </si>
-  <si>
     <t>SUMATERA UTARA</t>
   </si>
   <si>
     <t>KEPULAUAN RIAU</t>
+  </si>
+  <si>
+    <t>TARIF HOTEL PEJABAT NEGARA / PEJABAT ESELON I</t>
+  </si>
+  <si>
+    <t>TARIF HOTEL PEJABAT NEGARA LAINNYA / PEJABAT ESELON II</t>
+  </si>
+  <si>
+    <t>TARIF HOTEL PEJABAT ESELON III / GOLONGAN IV</t>
+  </si>
+  <si>
+    <t>TARIF HOTEL PEJABAT ESELON IV / GOLONGAN III  / II / I</t>
   </si>
 </sst>
 </file>
@@ -217,7 +214,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -251,56 +248,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -316,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -324,13 +271,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -339,31 +286,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -680,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1B877B4-8CEF-425B-A03C-ADEFD6F1493E}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35.88671875" customWidth="1"/>
@@ -705,7 +640,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="7"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -715,565 +650,577 @@
       <c r="C2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="16"/>
-    </row>
-    <row r="3" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="G2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>-1</v>
+      </c>
+      <c r="B3" s="8">
+        <v>-2</v>
+      </c>
+      <c r="C3" s="9">
+        <v>-3</v>
+      </c>
+      <c r="D3" s="8">
+        <v>-4</v>
+      </c>
+      <c r="E3" s="8">
+        <v>-5</v>
+      </c>
+      <c r="F3" s="8">
+        <v>-6</v>
+      </c>
+      <c r="G3" s="8">
+        <v>-7</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
-        <v>-1</v>
-      </c>
-      <c r="B4" s="8">
-        <v>-2</v>
-      </c>
-      <c r="C4" s="9">
-        <v>-3</v>
-      </c>
-      <c r="D4" s="8">
-        <v>-4</v>
-      </c>
-      <c r="E4" s="8">
-        <v>-5</v>
-      </c>
-      <c r="F4" s="8">
-        <v>-6</v>
-      </c>
-      <c r="G4" s="8">
-        <v>-7</v>
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="11">
+        <v>4774000</v>
+      </c>
+      <c r="E4" s="11">
+        <v>3526000</v>
+      </c>
+      <c r="F4" s="11">
+        <v>1578000</v>
+      </c>
+      <c r="G4" s="11">
+        <v>770000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="11">
-        <v>4774000</v>
+        <v>4960000</v>
       </c>
       <c r="E5" s="11">
-        <v>3526000</v>
+        <v>2195000</v>
       </c>
       <c r="F5" s="11">
-        <v>1578000</v>
+        <v>1188000</v>
       </c>
       <c r="G5" s="11">
-        <v>770000</v>
+        <v>699000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="11">
-        <v>4960000</v>
+        <v>3820000</v>
       </c>
       <c r="E6" s="11">
-        <v>2195000</v>
+        <v>3119000</v>
       </c>
       <c r="F6" s="11">
-        <v>1188000</v>
+        <v>1650000</v>
       </c>
       <c r="G6" s="11">
-        <v>699000</v>
+        <v>852000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="11">
-        <v>3820000</v>
+        <v>5772000</v>
       </c>
       <c r="E7" s="11">
-        <v>3119000</v>
+        <v>2318000</v>
       </c>
       <c r="F7" s="11">
-        <v>1650000</v>
+        <v>1297000</v>
       </c>
       <c r="G7" s="11">
-        <v>852000</v>
+        <v>792000</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="11">
-        <v>5772000</v>
+        <v>5004000</v>
       </c>
       <c r="E8" s="11">
-        <v>2318000</v>
+        <v>4102000</v>
       </c>
       <c r="F8" s="11">
-        <v>1297000</v>
+        <v>1225000</v>
       </c>
       <c r="G8" s="11">
-        <v>792000</v>
+        <v>580000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="11">
-        <v>5004000</v>
+        <v>5236000</v>
       </c>
       <c r="E9" s="11">
-        <v>4102000</v>
+        <v>3332000</v>
       </c>
       <c r="F9" s="11">
-        <v>1225000</v>
+        <v>1353000</v>
       </c>
       <c r="G9" s="11">
-        <v>580000</v>
+        <v>701000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="11">
-        <v>5236000</v>
+        <v>6298000</v>
       </c>
       <c r="E10" s="11">
-        <v>3332000</v>
+        <v>3083000</v>
       </c>
       <c r="F10" s="11">
-        <v>1353000</v>
+        <v>1966000</v>
       </c>
       <c r="G10" s="11">
-        <v>701000</v>
+        <v>861000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="11">
-        <v>6298000</v>
+        <v>4491000</v>
       </c>
       <c r="E11" s="11">
-        <v>3083000</v>
+        <v>2488000</v>
       </c>
       <c r="F11" s="11">
-        <v>1966000</v>
+        <v>1539000</v>
       </c>
       <c r="G11" s="11">
-        <v>861000</v>
+        <v>580000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="11">
-        <v>4491000</v>
+        <v>2140000</v>
       </c>
       <c r="E12" s="11">
-        <v>2488000</v>
+        <v>1628000</v>
       </c>
       <c r="F12" s="11">
-        <v>1539000</v>
+        <v>1546000</v>
       </c>
       <c r="G12" s="11">
-        <v>580000</v>
+        <v>692000</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="11">
-        <v>2140000</v>
+        <v>4134000</v>
       </c>
       <c r="E13" s="11">
-        <v>1628000</v>
+        <v>2838000</v>
       </c>
       <c r="F13" s="11">
-        <v>1546000</v>
+        <v>1957000</v>
       </c>
       <c r="G13" s="11">
-        <v>692000</v>
+        <v>676000</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="11">
-        <v>4134000</v>
+        <v>5725000</v>
       </c>
       <c r="E14" s="11">
-        <v>2838000</v>
+        <v>2373000</v>
       </c>
       <c r="F14" s="11">
-        <v>1957000</v>
+        <v>1301000</v>
       </c>
       <c r="G14" s="11">
-        <v>676000</v>
+        <v>724000</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="11">
-        <v>5725000</v>
+        <v>5812000</v>
       </c>
       <c r="E15" s="11">
-        <v>2373000</v>
+        <v>2755000</v>
       </c>
       <c r="F15" s="11">
-        <v>1301000</v>
+        <v>1298000</v>
       </c>
       <c r="G15" s="11">
-        <v>724000</v>
+        <v>686000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="11">
-        <v>5812000</v>
+        <v>8720000</v>
       </c>
       <c r="E16" s="11">
-        <v>2755000</v>
+        <v>2063000</v>
       </c>
       <c r="F16" s="11">
-        <v>1298000</v>
+        <v>992000</v>
       </c>
       <c r="G16" s="11">
-        <v>686000</v>
+        <v>730000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="11">
-        <v>8720000</v>
+        <v>5728000</v>
       </c>
       <c r="E17" s="11">
-        <v>2063000</v>
+        <v>1998000</v>
       </c>
       <c r="F17" s="11">
-        <v>992000</v>
+        <v>1201000</v>
       </c>
       <c r="G17" s="11">
-        <v>730000</v>
+        <v>810000</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="11">
-        <v>5728000</v>
+        <v>5017000</v>
       </c>
       <c r="E18" s="11">
-        <v>1998000</v>
+        <v>2695000</v>
       </c>
       <c r="F18" s="11">
-        <v>1201000</v>
+        <v>1495000</v>
       </c>
       <c r="G18" s="11">
-        <v>810000</v>
+        <v>845000</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="11">
-        <v>5017000</v>
+        <v>4449000</v>
       </c>
       <c r="E19" s="11">
-        <v>2695000</v>
+        <v>2007000</v>
       </c>
       <c r="F19" s="11">
-        <v>1495000</v>
+        <v>1153000</v>
       </c>
       <c r="G19" s="11">
-        <v>845000</v>
+        <v>814000</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="11">
-        <v>4449000</v>
+        <v>6848000</v>
       </c>
       <c r="E20" s="11">
-        <v>2007000</v>
+        <v>2433000</v>
       </c>
       <c r="F20" s="11">
-        <v>1153000</v>
+        <v>1685000</v>
       </c>
       <c r="G20" s="11">
-        <v>814000</v>
+        <v>1138000</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="11">
-        <v>6848000</v>
+        <v>4375000</v>
       </c>
       <c r="E21" s="11">
-        <v>2433000</v>
+        <v>2648000</v>
       </c>
       <c r="F21" s="11">
-        <v>1685000</v>
+        <v>1418000</v>
       </c>
       <c r="G21" s="11">
-        <v>1138000</v>
+        <v>907000</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="11">
-        <v>4375000</v>
+        <v>3750000</v>
       </c>
       <c r="E22" s="11">
-        <v>2648000</v>
+        <v>2133000</v>
       </c>
       <c r="F22" s="11">
-        <v>1418000</v>
+        <v>1355000</v>
       </c>
       <c r="G22" s="11">
-        <v>907000</v>
+        <v>688000</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="11">
-        <v>3750000</v>
+        <v>2654000</v>
       </c>
       <c r="E23" s="11">
-        <v>2133000</v>
+        <v>1923000</v>
       </c>
       <c r="F23" s="11">
-        <v>1355000</v>
+        <v>1125000</v>
       </c>
       <c r="G23" s="11">
-        <v>688000</v>
+        <v>538000</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="11">
-        <v>2654000</v>
+        <v>4901000</v>
       </c>
       <c r="E24" s="11">
-        <v>1923000</v>
+        <v>3391000</v>
       </c>
       <c r="F24" s="11">
-        <v>1125000</v>
+        <v>1160000</v>
       </c>
       <c r="G24" s="11">
-        <v>538000</v>
+        <v>659000</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="11">
-        <v>4901000</v>
+        <v>4797000</v>
       </c>
       <c r="E25" s="11">
-        <v>3391000</v>
+        <v>3316000</v>
       </c>
       <c r="F25" s="11">
-        <v>1160000</v>
+        <v>1500000</v>
       </c>
       <c r="G25" s="11">
-        <v>659000</v>
+        <v>697000</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="11">
-        <v>4797000</v>
+        <v>4000000</v>
       </c>
       <c r="E26" s="11">
-        <v>3316000</v>
+        <v>2188000</v>
       </c>
       <c r="F26" s="11">
-        <v>1500000</v>
+        <v>1507000</v>
       </c>
       <c r="G26" s="11">
-        <v>697000</v>
+        <v>804000</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
@@ -1282,251 +1229,251 @@
         <v>4000000</v>
       </c>
       <c r="E27" s="11">
-        <v>2188000</v>
+        <v>2735000</v>
       </c>
       <c r="F27" s="11">
         <v>1507000</v>
       </c>
       <c r="G27" s="11">
-        <v>804000</v>
+        <v>904000</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="11">
-        <v>4000000</v>
+        <v>4919000</v>
       </c>
       <c r="E28" s="11">
-        <v>2735000</v>
+        <v>2290000</v>
       </c>
       <c r="F28" s="11">
-        <v>1507000</v>
+        <v>1270000</v>
       </c>
       <c r="G28" s="11">
-        <v>904000</v>
+        <v>978000</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="11">
-        <v>4919000</v>
+        <v>4168000</v>
       </c>
       <c r="E29" s="11">
-        <v>2290000</v>
+        <v>3107000</v>
       </c>
       <c r="F29" s="11">
-        <v>1270000</v>
+        <v>1606000</v>
       </c>
       <c r="G29" s="11">
-        <v>978000</v>
+        <v>955000</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="11">
-        <v>4168000</v>
+        <v>4076000</v>
       </c>
       <c r="E30" s="11">
-        <v>3107000</v>
+        <v>3098000</v>
       </c>
       <c r="F30" s="11">
-        <v>1606000</v>
+        <v>1344000</v>
       </c>
       <c r="G30" s="11">
-        <v>955000</v>
+        <v>704000</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D31" s="11">
-        <v>4076000</v>
+        <v>4820000</v>
       </c>
       <c r="E31" s="11">
-        <v>3098000</v>
+        <v>1938000</v>
       </c>
       <c r="F31" s="11">
-        <v>1344000</v>
+        <v>1423000</v>
       </c>
       <c r="G31" s="11">
-        <v>704000</v>
+        <v>745000</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D32" s="11">
-        <v>4820000</v>
+        <v>2309000</v>
       </c>
       <c r="E32" s="11">
-        <v>1938000</v>
+        <v>2027000</v>
       </c>
       <c r="F32" s="11">
-        <v>1423000</v>
+        <v>1679000</v>
       </c>
       <c r="G32" s="11">
-        <v>745000</v>
+        <v>951000</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D33" s="11">
-        <v>2309000</v>
+        <v>3089000</v>
       </c>
       <c r="E33" s="11">
-        <v>2027000</v>
+        <v>2574000</v>
       </c>
       <c r="F33" s="11">
-        <v>1679000</v>
+        <v>1297000</v>
       </c>
       <c r="G33" s="11">
-        <v>951000</v>
+        <v>786000</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D34" s="11">
-        <v>3089000</v>
+        <v>3467000</v>
       </c>
       <c r="E34" s="11">
-        <v>2574000</v>
+        <v>3240000</v>
       </c>
       <c r="F34" s="11">
-        <v>1297000</v>
+        <v>1059000</v>
       </c>
       <c r="G34" s="11">
-        <v>786000</v>
+        <v>667000</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D35" s="11">
-        <v>3467000</v>
+        <v>4612000</v>
       </c>
       <c r="E35" s="11">
-        <v>3240000</v>
+        <v>3843000</v>
       </c>
       <c r="F35" s="11">
-        <v>1059000</v>
+        <v>1160000</v>
       </c>
       <c r="G35" s="11">
-        <v>667000</v>
+        <v>654000</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="11">
-        <v>4612000</v>
+        <v>3859000</v>
       </c>
       <c r="E36" s="11">
-        <v>3843000</v>
+        <v>3318000</v>
       </c>
       <c r="F36" s="11">
-        <v>1160000</v>
+        <v>2521000</v>
       </c>
       <c r="G36" s="11">
-        <v>654000</v>
+        <v>1038000</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D37" s="11">
-        <v>3859000</v>
+        <v>3872000</v>
       </c>
       <c r="E37" s="11">
-        <v>3318000</v>
+        <v>3341000</v>
       </c>
       <c r="F37" s="11">
-        <v>2521000</v>
+        <v>2056000</v>
       </c>
       <c r="G37" s="11">
-        <v>1038000</v>
+        <v>967000</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
@@ -1546,103 +1493,74 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="11">
-        <v>3872000</v>
+        <v>3859000</v>
       </c>
       <c r="E39" s="11">
-        <v>3341000</v>
+        <v>3318000</v>
       </c>
       <c r="F39" s="11">
-        <v>2056000</v>
+        <v>2521000</v>
       </c>
       <c r="G39" s="11">
-        <v>967000</v>
+        <v>1038000</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D40" s="11">
-        <v>3859000</v>
+        <v>5673000</v>
       </c>
       <c r="E40" s="11">
-        <v>3318000</v>
+        <v>4877000</v>
       </c>
       <c r="F40" s="11">
-        <v>2521000</v>
+        <v>3706000</v>
       </c>
       <c r="G40" s="11">
-        <v>1038000</v>
+        <v>1526000</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D41" s="11">
-        <v>5673000</v>
+        <v>5711000</v>
       </c>
       <c r="E41" s="11">
-        <v>4877000</v>
+        <v>4911000</v>
       </c>
       <c r="F41" s="11">
-        <v>3706000</v>
+        <v>3731000</v>
       </c>
       <c r="G41" s="11">
-        <v>1526000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="10">
-        <v>38</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="11">
-        <v>5711000</v>
-      </c>
-      <c r="E42" s="11">
-        <v>4911000</v>
-      </c>
-      <c r="F42" s="11">
-        <v>3731000</v>
-      </c>
-      <c r="G42" s="11">
         <v>1536000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:G2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>